--- a/eagle/bom/reva_pnp_jlc.xlsx
+++ b/eagle/bom/reva_pnp_jlc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wpi0-my.sharepoint.com/personal/jwbuchta_wpi_edu/Documents/Jobs/academic_technician/flashing_led/eagle/bom/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="11_F25DC773A252ABDACC10483079DB61465BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{226ADA5F-8FFF-4296-BB0F-1169FAC3DA2E}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="11_F25DC773A252ABDACC10483079DB61465BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2F566DE-792F-47A4-B921-ABBF92F2E9C0}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3917,7 +3917,7 @@
         <v>9</v>
       </c>
       <c r="D163">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="E163" t="s">
         <v>165</v>

--- a/eagle/bom/reva_pnp_jlc.xlsx
+++ b/eagle/bom/reva_pnp_jlc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wpi0-my.sharepoint.com/personal/jwbuchta_wpi_edu/Documents/Jobs/academic_technician/flashing_led/eagle/bom/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="11_F25DC773A252ABDACC10483079DB61465BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2F566DE-792F-47A4-B921-ABBF92F2E9C0}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="11_F25DC773A252ABDACC10483079DB61465BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4032D82-FA1D-4D81-AEF4-D880882D3FE5}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2945,7 +2945,7 @@
         <v>71</v>
       </c>
       <c r="C106">
-        <v>6.75</v>
+        <v>4.25</v>
       </c>
       <c r="D106">
         <v>0</v>

--- a/eagle/bom/reva_pnp_jlc.xlsx
+++ b/eagle/bom/reva_pnp_jlc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wpi0-my.sharepoint.com/personal/jwbuchta_wpi_edu/Documents/Jobs/academic_technician/flashing_led/eagle/bom/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="11_F25DC773A252ABDACC10483079DB61465BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4032D82-FA1D-4D81-AEF4-D880882D3FE5}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="11_F25DC773A252ABDACC10483079DB61465BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33B6968F-A758-4EE5-9C66-8A6E8C3D9937}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="PnP_reva_front" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="0" hidden="1">PnP_reva_front!$A$1:$E$163</definedName>
+    <definedName name="ExternalData_1" localSheetId="0" hidden="1">PnP_reva_front!$A$1:$E$164</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="235">
   <si>
     <t>C2</t>
   </si>
@@ -59,9 +59,6 @@
     <t>C8</t>
   </si>
   <si>
-    <t>C9</t>
-  </si>
-  <si>
     <t>DA10</t>
   </si>
   <si>
@@ -741,6 +738,12 @@
   </si>
   <si>
     <t>PWR</t>
+  </si>
+  <si>
+    <t>R76</t>
+  </si>
+  <si>
+    <t>R110</t>
   </si>
 </sst>
 </file>
@@ -770,7 +773,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -802,31 +805,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
-      </right>
-      <top style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -853,7 +841,7 @@
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="2" xr16:uid="{303889ED-B786-4607-86B9-4F97E5E0425C}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
+  <queryTableRefresh nextId="8">
     <queryTableFields count="5">
       <queryTableField id="1" name="Column1" tableColumnId="1"/>
       <queryTableField id="2" name="Column2" tableColumnId="2"/>
@@ -869,8 +857,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CFB85CB0-00E1-4581-BC3B-3ECA244FFF47}" name="PnP_reva_front" displayName="PnP_reva_front" ref="A1:E163" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:E163" xr:uid="{CFB85CB0-00E1-4581-BC3B-3ECA244FFF47}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CFB85CB0-00E1-4581-BC3B-3ECA244FFF47}" name="PnP_reva_front" displayName="PnP_reva_front" ref="A1:E164" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:E164" xr:uid="{CFB85CB0-00E1-4581-BC3B-3ECA244FFF47}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{FA11D59F-05C6-49FE-804B-FF9A010DC16C}" uniqueName="1" name="Designator" queryTableFieldId="1" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{7AA84A36-99CC-49DA-B23D-3E365889D30D}" uniqueName="2" name="Mid X" queryTableFieldId="2"/>
@@ -1145,7 +1133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97721062-57F2-437D-863B-19CCBDDD1FD9}">
-  <dimension ref="A1:F228"/>
+  <dimension ref="A1:E229"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="4" width="10.15625" bestFit="1" customWidth="1"/>
@@ -1154,197 +1142,197 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B1" t="s">
         <v>160</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>161</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>162</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>163</v>
-      </c>
-      <c r="E1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B2">
-        <v>68</v>
+        <v>52.4</v>
       </c>
       <c r="C2">
-        <v>39.9</v>
+        <v>13.4</v>
       </c>
       <c r="D2">
         <v>180</v>
       </c>
       <c r="E2" t="s">
-        <v>231</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B3">
-        <v>71</v>
+        <v>55.3</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>13.4</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E3" t="s">
-        <v>231</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="B4">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="C4">
-        <v>9</v>
+        <v>39.9</v>
       </c>
       <c r="D4">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E4" t="s">
-        <v>165</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>1</v>
+        <v>232</v>
       </c>
       <c r="B5">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="C5">
-        <v>14.2</v>
+        <v>10</v>
       </c>
       <c r="D5">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>165</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B6">
-        <v>11.5</v>
+        <v>54</v>
       </c>
       <c r="C6">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B7">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>12.5</v>
+        <v>14.2</v>
       </c>
       <c r="D7">
         <v>180</v>
       </c>
       <c r="E7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B8">
-        <v>60.5</v>
+        <v>11.5</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="D8">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B9">
-        <v>52</v>
+        <v>58.1</v>
       </c>
       <c r="C9">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="D9">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B10">
-        <v>53</v>
+        <v>60.5</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D10">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B11">
-        <v>44.55</v>
+        <v>52</v>
       </c>
       <c r="C11">
-        <v>45.15</v>
+        <v>9</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B12">
-        <v>49.05</v>
+        <v>44.55</v>
       </c>
       <c r="C12">
         <v>45.15</v>
@@ -1353,15 +1341,15 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B13">
-        <v>53.55</v>
+        <v>49.05</v>
       </c>
       <c r="C13">
         <v>45.15</v>
@@ -1370,15 +1358,15 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B14">
-        <v>58.05</v>
+        <v>53.55</v>
       </c>
       <c r="C14">
         <v>45.15</v>
@@ -1387,15 +1375,15 @@
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B15">
-        <v>62.55</v>
+        <v>58.05</v>
       </c>
       <c r="C15">
         <v>45.15</v>
@@ -1404,15 +1392,15 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B16">
-        <v>67.05</v>
+        <v>62.55</v>
       </c>
       <c r="C16">
         <v>45.15</v>
@@ -1421,15 +1409,15 @@
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B17">
-        <v>71.55</v>
+        <v>67.05</v>
       </c>
       <c r="C17">
         <v>45.15</v>
@@ -1438,15 +1426,15 @@
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B18">
-        <v>76.05</v>
+        <v>71.55</v>
       </c>
       <c r="C18">
         <v>45.15</v>
@@ -1455,15 +1443,15 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B19">
-        <v>80.55</v>
+        <v>76.05</v>
       </c>
       <c r="C19">
         <v>45.15</v>
@@ -1472,15 +1460,15 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B20">
-        <v>85.05</v>
+        <v>80.55</v>
       </c>
       <c r="C20">
         <v>45.15</v>
@@ -1489,15 +1477,15 @@
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B21">
-        <v>8.5500000000000007</v>
+        <v>85.05</v>
       </c>
       <c r="C21">
         <v>45.15</v>
@@ -1506,15 +1494,15 @@
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B22">
-        <v>13.05</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="C22">
         <v>45.15</v>
@@ -1523,15 +1511,15 @@
         <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B23">
-        <v>17.55</v>
+        <v>13.05</v>
       </c>
       <c r="C23">
         <v>45.15</v>
@@ -1540,15 +1528,15 @@
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B24">
-        <v>22.05</v>
+        <v>17.55</v>
       </c>
       <c r="C24">
         <v>45.15</v>
@@ -1557,15 +1545,15 @@
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B25">
-        <v>26.55</v>
+        <v>22.05</v>
       </c>
       <c r="C25">
         <v>45.15</v>
@@ -1574,15 +1562,15 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B26">
-        <v>31.05</v>
+        <v>26.55</v>
       </c>
       <c r="C26">
         <v>45.15</v>
@@ -1591,15 +1579,15 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B27">
-        <v>35.549999999999997</v>
+        <v>31.05</v>
       </c>
       <c r="C27">
         <v>45.15</v>
@@ -1608,15 +1596,15 @@
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B28">
-        <v>40.049999999999997</v>
+        <v>35.549999999999997</v>
       </c>
       <c r="C28">
         <v>45.15</v>
@@ -1625,32 +1613,32 @@
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B29">
-        <v>4.05</v>
+        <v>40.049999999999997</v>
       </c>
       <c r="C29">
-        <v>40.65</v>
+        <v>45.15</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B30">
-        <v>49.05</v>
+        <v>4.05</v>
       </c>
       <c r="C30">
         <v>40.65</v>
@@ -1659,15 +1647,15 @@
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B31">
-        <v>53.55</v>
+        <v>49.05</v>
       </c>
       <c r="C31">
         <v>40.65</v>
@@ -1676,15 +1664,15 @@
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B32">
-        <v>62.55</v>
+        <v>53.55</v>
       </c>
       <c r="C32">
         <v>40.65</v>
@@ -1693,15 +1681,15 @@
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B33">
-        <v>67.05</v>
+        <v>62.55</v>
       </c>
       <c r="C33">
         <v>40.65</v>
@@ -1710,15 +1698,15 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B34">
-        <v>71.55</v>
+        <v>67.05</v>
       </c>
       <c r="C34">
         <v>40.65</v>
@@ -1727,15 +1715,15 @@
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B35">
-        <v>8.5500000000000007</v>
+        <v>71.55</v>
       </c>
       <c r="C35">
         <v>40.65</v>
@@ -1744,15 +1732,15 @@
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B36">
-        <v>17.55</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="C36">
         <v>40.65</v>
@@ -1761,15 +1749,15 @@
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B37">
-        <v>26.55</v>
+        <v>17.55</v>
       </c>
       <c r="C37">
         <v>40.65</v>
@@ -1778,15 +1766,15 @@
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B38">
-        <v>35.549999999999997</v>
+        <v>26.55</v>
       </c>
       <c r="C38">
         <v>40.65</v>
@@ -1795,15 +1783,15 @@
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B39">
-        <v>40.049999999999997</v>
+        <v>35.549999999999997</v>
       </c>
       <c r="C39">
         <v>40.65</v>
@@ -1812,32 +1800,32 @@
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B40">
-        <v>53.55</v>
+        <v>40.049999999999997</v>
       </c>
       <c r="C40">
-        <v>36.15</v>
+        <v>40.65</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B41">
-        <v>62.55</v>
+        <v>53.55</v>
       </c>
       <c r="C41">
         <v>36.15</v>
@@ -1846,15 +1834,15 @@
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B42">
-        <v>67.05</v>
+        <v>62.55</v>
       </c>
       <c r="C42">
         <v>36.15</v>
@@ -1863,15 +1851,15 @@
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B43">
-        <v>71.55</v>
+        <v>67.05</v>
       </c>
       <c r="C43">
         <v>36.15</v>
@@ -1880,15 +1868,15 @@
         <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B44">
-        <v>76.05</v>
+        <v>71.55</v>
       </c>
       <c r="C44">
         <v>36.15</v>
@@ -1897,15 +1885,15 @@
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B45">
-        <v>80.55</v>
+        <v>76.05</v>
       </c>
       <c r="C45">
         <v>36.15</v>
@@ -1914,15 +1902,15 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B46">
-        <v>8.5500000000000007</v>
+        <v>80.55</v>
       </c>
       <c r="C46">
         <v>36.15</v>
@@ -1931,15 +1919,15 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B47">
-        <v>17.55</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="C47">
         <v>36.15</v>
@@ -1948,15 +1936,15 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B48">
-        <v>26.55</v>
+        <v>17.55</v>
       </c>
       <c r="C48">
         <v>36.15</v>
@@ -1965,15 +1953,15 @@
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B49">
-        <v>35.549999999999997</v>
+        <v>26.55</v>
       </c>
       <c r="C49">
         <v>36.15</v>
@@ -1982,15 +1970,15 @@
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B50">
-        <v>40.049999999999997</v>
+        <v>35.549999999999997</v>
       </c>
       <c r="C50">
         <v>36.15</v>
@@ -1999,32 +1987,32 @@
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B51">
-        <v>44.55</v>
+        <v>40.049999999999997</v>
       </c>
       <c r="C51">
-        <v>31.65</v>
+        <v>36.15</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B52">
-        <v>49.05</v>
+        <v>44.55</v>
       </c>
       <c r="C52">
         <v>31.65</v>
@@ -2033,15 +2021,15 @@
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B53">
-        <v>58.05</v>
+        <v>49.05</v>
       </c>
       <c r="C53">
         <v>31.65</v>
@@ -2050,15 +2038,15 @@
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B54">
-        <v>62.55</v>
+        <v>58.05</v>
       </c>
       <c r="C54">
         <v>31.65</v>
@@ -2067,15 +2055,15 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B55">
-        <v>67.05</v>
+        <v>62.55</v>
       </c>
       <c r="C55">
         <v>31.65</v>
@@ -2084,15 +2072,15 @@
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B56">
-        <v>71.55</v>
+        <v>67.05</v>
       </c>
       <c r="C56">
         <v>31.65</v>
@@ -2101,15 +2089,15 @@
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B57">
-        <v>76.05</v>
+        <v>71.55</v>
       </c>
       <c r="C57">
         <v>31.65</v>
@@ -2118,15 +2106,15 @@
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B58">
-        <v>85.05</v>
+        <v>76.05</v>
       </c>
       <c r="C58">
         <v>31.65</v>
@@ -2135,15 +2123,15 @@
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B59">
-        <v>8.5500000000000007</v>
+        <v>85.05</v>
       </c>
       <c r="C59">
         <v>31.65</v>
@@ -2152,15 +2140,15 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B60">
-        <v>13.05</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="C60">
         <v>31.65</v>
@@ -2169,15 +2157,15 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B61">
-        <v>17.55</v>
+        <v>13.05</v>
       </c>
       <c r="C61">
         <v>31.65</v>
@@ -2186,15 +2174,15 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B62">
-        <v>22.05</v>
+        <v>17.55</v>
       </c>
       <c r="C62">
         <v>31.65</v>
@@ -2203,15 +2191,15 @@
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B63">
-        <v>26.55</v>
+        <v>22.05</v>
       </c>
       <c r="C63">
         <v>31.65</v>
@@ -2220,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B64">
-        <v>35.549999999999997</v>
+        <v>26.55</v>
       </c>
       <c r="C64">
         <v>31.65</v>
@@ -2237,15 +2225,15 @@
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B65">
-        <v>40.049999999999997</v>
+        <v>35.549999999999997</v>
       </c>
       <c r="C65">
         <v>31.65</v>
@@ -2254,32 +2242,32 @@
         <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B66">
-        <v>53.55</v>
+        <v>40.049999999999997</v>
       </c>
       <c r="C66">
-        <v>27.15</v>
+        <v>31.65</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B67">
-        <v>62.55</v>
+        <v>53.55</v>
       </c>
       <c r="C67">
         <v>27.15</v>
@@ -2288,15 +2276,15 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B68">
-        <v>67.05</v>
+        <v>62.55</v>
       </c>
       <c r="C68">
         <v>27.15</v>
@@ -2305,15 +2293,15 @@
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B69">
-        <v>85.05</v>
+        <v>67.05</v>
       </c>
       <c r="C69">
         <v>27.15</v>
@@ -2322,15 +2310,15 @@
         <v>0</v>
       </c>
       <c r="E69" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B70">
-        <v>8.5500000000000007</v>
+        <v>85.05</v>
       </c>
       <c r="C70">
         <v>27.15</v>
@@ -2339,15 +2327,15 @@
         <v>0</v>
       </c>
       <c r="E70" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B71">
-        <v>17.55</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="C71">
         <v>27.15</v>
@@ -2356,15 +2344,15 @@
         <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B72">
-        <v>26.55</v>
+        <v>17.55</v>
       </c>
       <c r="C72">
         <v>27.15</v>
@@ -2373,15 +2361,15 @@
         <v>0</v>
       </c>
       <c r="E72" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B73">
-        <v>31.05</v>
+        <v>26.55</v>
       </c>
       <c r="C73">
         <v>27.15</v>
@@ -2390,15 +2378,15 @@
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B74">
-        <v>35.549999999999997</v>
+        <v>31.05</v>
       </c>
       <c r="C74">
         <v>27.15</v>
@@ -2407,15 +2395,15 @@
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B75">
-        <v>40.049999999999997</v>
+        <v>35.549999999999997</v>
       </c>
       <c r="C75">
         <v>27.15</v>
@@ -2424,32 +2412,32 @@
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B76">
-        <v>4.05</v>
+        <v>40.049999999999997</v>
       </c>
       <c r="C76">
-        <v>22.65</v>
+        <v>27.15</v>
       </c>
       <c r="D76">
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B77">
-        <v>49.05</v>
+        <v>4.05</v>
       </c>
       <c r="C77">
         <v>22.65</v>
@@ -2458,15 +2446,15 @@
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B78">
-        <v>53.55</v>
+        <v>49.05</v>
       </c>
       <c r="C78">
         <v>22.65</v>
@@ -2475,15 +2463,15 @@
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B79">
-        <v>62.55</v>
+        <v>53.55</v>
       </c>
       <c r="C79">
         <v>22.65</v>
@@ -2492,15 +2480,15 @@
         <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B80">
-        <v>67.05</v>
+        <v>62.55</v>
       </c>
       <c r="C80">
         <v>22.65</v>
@@ -2509,15 +2497,15 @@
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B81">
-        <v>85.05</v>
+        <v>67.05</v>
       </c>
       <c r="C81">
         <v>22.65</v>
@@ -2526,15 +2514,15 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B82">
-        <v>8.5500000000000007</v>
+        <v>85.05</v>
       </c>
       <c r="C82">
         <v>22.65</v>
@@ -2543,15 +2531,15 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B83">
-        <v>17.55</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="C83">
         <v>22.65</v>
@@ -2560,15 +2548,15 @@
         <v>0</v>
       </c>
       <c r="E83" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B84">
-        <v>26.55</v>
+        <v>17.55</v>
       </c>
       <c r="C84">
         <v>22.65</v>
@@ -2577,15 +2565,15 @@
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B85">
-        <v>35.549999999999997</v>
+        <v>26.55</v>
       </c>
       <c r="C85">
         <v>22.65</v>
@@ -2594,15 +2582,15 @@
         <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B86">
-        <v>40.049999999999997</v>
+        <v>35.549999999999997</v>
       </c>
       <c r="C86">
         <v>22.65</v>
@@ -2611,32 +2599,32 @@
         <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B87">
-        <v>4.05</v>
+        <v>40.049999999999997</v>
       </c>
       <c r="C87">
-        <v>18.149999999999999</v>
+        <v>22.65</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B88">
-        <v>44.55</v>
+        <v>4.05</v>
       </c>
       <c r="C88">
         <v>18.149999999999999</v>
@@ -2645,15 +2633,15 @@
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B89">
-        <v>49.05</v>
+        <v>44.55</v>
       </c>
       <c r="C89">
         <v>18.149999999999999</v>
@@ -2662,15 +2650,15 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B90">
-        <v>53.55</v>
+        <v>49.05</v>
       </c>
       <c r="C90">
         <v>18.149999999999999</v>
@@ -2679,15 +2667,15 @@
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B91">
-        <v>58.05</v>
+        <v>53.55</v>
       </c>
       <c r="C91">
         <v>18.149999999999999</v>
@@ -2696,15 +2684,15 @@
         <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B92">
-        <v>62.55</v>
+        <v>58.05</v>
       </c>
       <c r="C92">
         <v>18.149999999999999</v>
@@ -2713,15 +2701,15 @@
         <v>0</v>
       </c>
       <c r="E92" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B93">
-        <v>67.05</v>
+        <v>62.55</v>
       </c>
       <c r="C93">
         <v>18.149999999999999</v>
@@ -2730,15 +2718,15 @@
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B94">
-        <v>71.55</v>
+        <v>67.05</v>
       </c>
       <c r="C94">
         <v>18.149999999999999</v>
@@ -2747,15 +2735,15 @@
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B95">
-        <v>76.05</v>
+        <v>71.55</v>
       </c>
       <c r="C95">
         <v>18.149999999999999</v>
@@ -2764,15 +2752,15 @@
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B96">
-        <v>80.55</v>
+        <v>76.05</v>
       </c>
       <c r="C96">
         <v>18.149999999999999</v>
@@ -2781,15 +2769,15 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B97">
-        <v>8.5500000000000007</v>
+        <v>80.55</v>
       </c>
       <c r="C97">
         <v>18.149999999999999</v>
@@ -2798,15 +2786,15 @@
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B98">
-        <v>13.05</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="C98">
         <v>18.149999999999999</v>
@@ -2815,15 +2803,15 @@
         <v>0</v>
       </c>
       <c r="E98" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B99">
-        <v>17.55</v>
+        <v>13.05</v>
       </c>
       <c r="C99">
         <v>18.149999999999999</v>
@@ -2832,15 +2820,15 @@
         <v>0</v>
       </c>
       <c r="E99" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B100">
-        <v>22.05</v>
+        <v>17.55</v>
       </c>
       <c r="C100">
         <v>18.149999999999999</v>
@@ -2849,15 +2837,15 @@
         <v>0</v>
       </c>
       <c r="E100" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B101">
-        <v>26.55</v>
+        <v>22.05</v>
       </c>
       <c r="C101">
         <v>18.149999999999999</v>
@@ -2866,15 +2854,15 @@
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B102">
-        <v>31.05</v>
+        <v>26.55</v>
       </c>
       <c r="C102">
         <v>18.149999999999999</v>
@@ -2883,15 +2871,15 @@
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B103">
-        <v>35.549999999999997</v>
+        <v>31.05</v>
       </c>
       <c r="C103">
         <v>18.149999999999999</v>
@@ -2900,15 +2888,15 @@
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B104">
-        <v>40.049999999999997</v>
+        <v>35.549999999999997</v>
       </c>
       <c r="C104">
         <v>18.149999999999999</v>
@@ -2917,83 +2905,83 @@
         <v>0</v>
       </c>
       <c r="E104" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B105">
-        <v>9</v>
+        <v>40.049999999999997</v>
       </c>
       <c r="C105">
-        <v>10.5</v>
+        <v>18.149999999999999</v>
       </c>
       <c r="D105">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="E105" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B106">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="C106">
-        <v>4.25</v>
+        <v>10.5</v>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="E106" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B107">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C107">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="D107">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="E107" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B108">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C108">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="D108">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E108" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B109">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C109">
         <v>8</v>
@@ -3002,15 +2990,15 @@
         <v>90</v>
       </c>
       <c r="E109" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B110">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C110">
         <v>8</v>
@@ -3019,32 +3007,32 @@
         <v>90</v>
       </c>
       <c r="E110" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B111">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C111">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="D111">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="E111" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B112">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C112">
         <v>4.2</v>
@@ -3053,15 +3041,15 @@
         <v>270</v>
       </c>
       <c r="E112" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B113">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C113">
         <v>4.2</v>
@@ -3070,32 +3058,32 @@
         <v>270</v>
       </c>
       <c r="E113" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B114">
-        <v>47.7</v>
+        <v>41</v>
       </c>
       <c r="C114">
-        <v>12.3</v>
+        <v>4.2</v>
       </c>
       <c r="D114">
         <v>270</v>
       </c>
       <c r="E114" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B115">
-        <v>41.4</v>
+        <v>47.7</v>
       </c>
       <c r="C115">
         <v>12.3</v>
@@ -3104,202 +3092,202 @@
         <v>270</v>
       </c>
       <c r="E115" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B116">
-        <v>37</v>
+        <v>41.4</v>
       </c>
       <c r="C116">
-        <v>13.5</v>
+        <v>12.3</v>
       </c>
       <c r="D116">
         <v>270</v>
       </c>
       <c r="E116" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B117">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C117">
-        <v>49</v>
+        <v>13.5</v>
       </c>
       <c r="D117">
         <v>270</v>
       </c>
       <c r="E117" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B118">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="C118">
-        <v>11.5</v>
+        <v>49</v>
       </c>
       <c r="D118">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="E118" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B119">
         <v>28</v>
       </c>
       <c r="C119">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="D119">
         <v>180</v>
       </c>
       <c r="E119" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B120">
-        <v>27.5</v>
+        <v>28</v>
       </c>
       <c r="C120">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="D120">
         <v>180</v>
       </c>
       <c r="E120" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B121">
         <v>27.5</v>
       </c>
       <c r="C121">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="D121">
         <v>180</v>
       </c>
       <c r="E121" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B122">
-        <v>22</v>
+        <v>27.5</v>
       </c>
       <c r="C122">
-        <v>8</v>
+        <v>3.7</v>
       </c>
       <c r="D122">
         <v>180</v>
       </c>
       <c r="E122" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B123">
         <v>22</v>
       </c>
       <c r="C123">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D123">
         <v>180</v>
       </c>
       <c r="E123" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B124">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="C124">
-        <v>6.9</v>
+        <v>12</v>
       </c>
       <c r="D124">
         <v>180</v>
       </c>
       <c r="E124" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B125">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C125">
-        <v>12.5</v>
+        <v>6.9</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E125" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B126">
-        <v>52.5</v>
+        <v>60.8</v>
       </c>
       <c r="C126">
-        <v>49</v>
+        <v>12.5</v>
       </c>
       <c r="D126">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E126" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B127">
-        <v>57</v>
+        <v>52.5</v>
       </c>
       <c r="C127">
         <v>49</v>
@@ -3308,15 +3296,15 @@
         <v>90</v>
       </c>
       <c r="E127" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B128">
-        <v>61.5</v>
+        <v>57</v>
       </c>
       <c r="C128">
         <v>49</v>
@@ -3325,15 +3313,15 @@
         <v>90</v>
       </c>
       <c r="E128" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B129">
-        <v>66</v>
+        <v>61.5</v>
       </c>
       <c r="C129">
         <v>49</v>
@@ -3342,15 +3330,15 @@
         <v>90</v>
       </c>
       <c r="E129" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B130">
-        <v>70.5</v>
+        <v>66</v>
       </c>
       <c r="C130">
         <v>49</v>
@@ -3359,15 +3347,15 @@
         <v>90</v>
       </c>
       <c r="E130" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B131">
-        <v>75</v>
+        <v>70.5</v>
       </c>
       <c r="C131">
         <v>49</v>
@@ -3376,15 +3364,15 @@
         <v>90</v>
       </c>
       <c r="E131" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B132">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C132">
         <v>49</v>
@@ -3393,15 +3381,15 @@
         <v>90</v>
       </c>
       <c r="E132" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B133">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C133">
         <v>49</v>
@@ -3410,185 +3398,185 @@
         <v>90</v>
       </c>
       <c r="E133" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B134">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C134">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D134">
         <v>90</v>
       </c>
       <c r="E134" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B135">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C135">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D135">
         <v>90</v>
       </c>
       <c r="E135" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B136">
-        <v>5.5</v>
+        <v>12</v>
       </c>
       <c r="C136">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D136">
         <v>90</v>
       </c>
       <c r="E136" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B137">
-        <v>46.5</v>
+        <v>5.5</v>
       </c>
       <c r="C137">
-        <v>40.5</v>
+        <v>45</v>
       </c>
       <c r="D137">
         <v>90</v>
       </c>
       <c r="E137" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B138">
-        <v>47.5</v>
+        <v>46.5</v>
       </c>
       <c r="C138">
-        <v>38</v>
+        <v>40.5</v>
       </c>
       <c r="D138">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="E138" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B139">
-        <v>60</v>
+        <v>47.5</v>
       </c>
       <c r="C139">
-        <v>40.5</v>
+        <v>38</v>
       </c>
       <c r="D139">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E139" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B140">
-        <v>56.8</v>
+        <v>60</v>
       </c>
       <c r="C140">
-        <v>42.1</v>
+        <v>40.5</v>
       </c>
       <c r="D140">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="E140" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B141">
-        <v>74.3</v>
+        <v>56.8</v>
       </c>
       <c r="C141">
-        <v>41.9</v>
+        <v>42.1</v>
       </c>
       <c r="D141">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E141" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B142">
-        <v>16.5</v>
+        <v>74.3</v>
       </c>
       <c r="C142">
-        <v>49</v>
+        <v>41.9</v>
       </c>
       <c r="D142">
         <v>90</v>
       </c>
       <c r="E142" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B143">
-        <v>51</v>
+        <v>16.5</v>
       </c>
       <c r="C143">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D143">
         <v>90</v>
       </c>
       <c r="E143" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B144">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C144">
         <v>36</v>
@@ -3597,117 +3585,117 @@
         <v>90</v>
       </c>
       <c r="E144" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B145">
-        <v>58.5</v>
+        <v>60</v>
       </c>
       <c r="C145">
         <v>36</v>
       </c>
       <c r="D145">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="E145" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B146">
-        <v>75.900000000000006</v>
+        <v>58.5</v>
       </c>
       <c r="C146">
-        <v>41.3</v>
+        <v>36</v>
       </c>
       <c r="D146">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="E146" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B147">
-        <v>81.900000000000006</v>
+        <v>75.900000000000006</v>
       </c>
       <c r="C147">
-        <v>40.4</v>
+        <v>41.3</v>
       </c>
       <c r="D147">
         <v>90</v>
       </c>
       <c r="E147" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B148">
-        <v>21</v>
+        <v>81.900000000000006</v>
       </c>
       <c r="C148">
-        <v>49</v>
+        <v>40.4</v>
       </c>
       <c r="D148">
         <v>90</v>
       </c>
       <c r="E148" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B149">
-        <v>83.4</v>
+        <v>21</v>
       </c>
       <c r="C149">
-        <v>40.4</v>
+        <v>49</v>
       </c>
       <c r="D149">
         <v>90</v>
       </c>
       <c r="E149" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B150">
-        <v>44.3</v>
+        <v>83.4</v>
       </c>
       <c r="C150">
-        <v>34</v>
+        <v>40.4</v>
       </c>
       <c r="D150">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E150" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B151">
-        <v>49</v>
+        <v>44.3</v>
       </c>
       <c r="C151">
         <v>34</v>
@@ -3716,151 +3704,151 @@
         <v>0</v>
       </c>
       <c r="E151" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B152">
-        <v>25.5</v>
+        <v>49</v>
       </c>
       <c r="C152">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D152">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E152" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B153">
-        <v>55.5</v>
+        <v>25.5</v>
       </c>
       <c r="C153">
-        <v>31.5</v>
+        <v>49</v>
       </c>
       <c r="D153">
         <v>90</v>
       </c>
       <c r="E153" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B154">
-        <v>58.5</v>
+        <v>55.5</v>
       </c>
       <c r="C154">
-        <v>28.5</v>
+        <v>31.5</v>
       </c>
       <c r="D154">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="E154" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B155">
-        <v>71.5</v>
+        <v>58.5</v>
       </c>
       <c r="C155">
-        <v>27.5</v>
+        <v>28.5</v>
       </c>
       <c r="D155">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E155" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B156">
         <v>71.5</v>
       </c>
       <c r="C156">
-        <v>29</v>
+        <v>27.5</v>
       </c>
       <c r="D156">
         <v>0</v>
       </c>
       <c r="E156" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B157">
-        <v>75</v>
+        <v>71.5</v>
       </c>
       <c r="C157">
-        <v>28.5</v>
+        <v>29</v>
       </c>
       <c r="D157">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="E157" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B158">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C158">
-        <v>32</v>
+        <v>28.5</v>
       </c>
       <c r="D158">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E158" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B159">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="C159">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D159">
         <v>90</v>
       </c>
       <c r="E159" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B160">
-        <v>34.5</v>
+        <v>30</v>
       </c>
       <c r="C160">
         <v>49</v>
@@ -3869,15 +3857,15 @@
         <v>90</v>
       </c>
       <c r="E160" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B161">
-        <v>39</v>
+        <v>34.5</v>
       </c>
       <c r="C161">
         <v>49</v>
@@ -3886,15 +3874,15 @@
         <v>90</v>
       </c>
       <c r="E161" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B162">
-        <v>43.5</v>
+        <v>39</v>
       </c>
       <c r="C162">
         <v>49</v>
@@ -3903,1195 +3891,1147 @@
         <v>90</v>
       </c>
       <c r="E162" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A163" t="s">
+        <v>157</v>
+      </c>
+      <c r="B163">
+        <v>43.5</v>
+      </c>
+      <c r="C163">
+        <v>49</v>
+      </c>
+      <c r="D163">
+        <v>90</v>
+      </c>
+      <c r="E163" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A164" t="s">
+        <v>158</v>
+      </c>
+      <c r="B164">
+        <v>57</v>
+      </c>
+      <c r="C164">
+        <v>9</v>
+      </c>
+      <c r="D164">
+        <v>0</v>
+      </c>
+      <c r="E164" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A165" s="3" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A163" t="s">
-        <v>159</v>
-      </c>
-      <c r="B163">
+      <c r="B165" s="1">
+        <v>29</v>
+      </c>
+      <c r="C165" s="1">
+        <v>14.5</v>
+      </c>
+      <c r="D165" s="1">
+        <v>180</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A166" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B166" s="2">
+        <v>15</v>
+      </c>
+      <c r="C166" s="2">
+        <v>7</v>
+      </c>
+      <c r="D166" s="2">
+        <v>270</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A167" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B167" s="1">
+        <v>25</v>
+      </c>
+      <c r="C167" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="D167" s="1">
+        <v>270</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A168" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B168" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="C168" s="2">
+        <v>45</v>
+      </c>
+      <c r="D168" s="2">
+        <v>90</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A169" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B169" s="1">
+        <v>45.9</v>
+      </c>
+      <c r="C169" s="1">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="D169" s="1">
+        <v>0</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A170" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B170" s="2">
+        <v>15.9</v>
+      </c>
+      <c r="C170" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="D170" s="2">
+        <v>90</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A171" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B171" s="1">
+        <v>16.5</v>
+      </c>
+      <c r="C171" s="1">
+        <v>40.5</v>
+      </c>
+      <c r="D171" s="1">
+        <v>90</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A172" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B172" s="2">
+        <v>25.5</v>
+      </c>
+      <c r="C172" s="2">
+        <v>40.5</v>
+      </c>
+      <c r="D172" s="2">
+        <v>90</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A173" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B173" s="1">
+        <v>34.5</v>
+      </c>
+      <c r="C173" s="1">
+        <v>40.5</v>
+      </c>
+      <c r="D173" s="1">
+        <v>90</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A174" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B174" s="2">
+        <v>39</v>
+      </c>
+      <c r="C174" s="2">
+        <v>40.5</v>
+      </c>
+      <c r="D174" s="2">
+        <v>90</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A175" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B175" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="C175" s="1">
+        <v>36</v>
+      </c>
+      <c r="D175" s="1">
+        <v>90</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A176" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B176" s="2">
+        <v>16.5</v>
+      </c>
+      <c r="C176" s="2">
+        <v>36</v>
+      </c>
+      <c r="D176" s="2">
+        <v>90</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A177" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B177" s="1">
+        <v>25.5</v>
+      </c>
+      <c r="C177" s="1">
+        <v>36</v>
+      </c>
+      <c r="D177" s="1">
+        <v>90</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A178" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B178" s="2">
+        <v>34.5</v>
+      </c>
+      <c r="C178" s="2">
+        <v>36</v>
+      </c>
+      <c r="D178" s="2">
+        <v>90</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A179" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B179" s="1">
+        <v>39</v>
+      </c>
+      <c r="C179" s="1">
+        <v>36</v>
+      </c>
+      <c r="D179" s="1">
+        <v>90</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A180" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B180" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="C180" s="2">
+        <v>31.5</v>
+      </c>
+      <c r="D180" s="2">
+        <v>90</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A181" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B181" s="1">
+        <v>12</v>
+      </c>
+      <c r="C181" s="1">
+        <v>31.5</v>
+      </c>
+      <c r="D181" s="1">
+        <v>90</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A182" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B182" s="2">
+        <v>16.5</v>
+      </c>
+      <c r="C182" s="2">
+        <v>31.5</v>
+      </c>
+      <c r="D182" s="2">
+        <v>90</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A183" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B183" s="1">
+        <v>21</v>
+      </c>
+      <c r="C183" s="1">
+        <v>31.5</v>
+      </c>
+      <c r="D183" s="1">
+        <v>90</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A184" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B184" s="2">
+        <v>25.5</v>
+      </c>
+      <c r="C184" s="2">
+        <v>31.5</v>
+      </c>
+      <c r="D184" s="2">
+        <v>90</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A185" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B185" s="1">
+        <v>34.5</v>
+      </c>
+      <c r="C185" s="1">
+        <v>31.5</v>
+      </c>
+      <c r="D185" s="1">
+        <v>90</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A186" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B186" s="2">
+        <v>39</v>
+      </c>
+      <c r="C186" s="2">
+        <v>31.5</v>
+      </c>
+      <c r="D186" s="2">
+        <v>90</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A187" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B187" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="C187" s="1">
+        <v>27</v>
+      </c>
+      <c r="D187" s="1">
+        <v>90</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A188" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B188" s="2">
+        <v>16.5</v>
+      </c>
+      <c r="C188" s="2">
+        <v>27</v>
+      </c>
+      <c r="D188" s="2">
+        <v>90</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A189" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B189" s="1">
+        <v>25.5</v>
+      </c>
+      <c r="C189" s="1">
+        <v>27</v>
+      </c>
+      <c r="D189" s="1">
+        <v>90</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A190" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B190" s="2">
+        <v>30</v>
+      </c>
+      <c r="C190" s="2">
+        <v>27</v>
+      </c>
+      <c r="D190" s="2">
+        <v>90</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A191" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B191" s="1">
+        <v>34.5</v>
+      </c>
+      <c r="C191" s="1">
+        <v>27</v>
+      </c>
+      <c r="D191" s="1">
+        <v>90</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A192" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B192" s="2">
+        <v>39</v>
+      </c>
+      <c r="C192" s="2">
+        <v>27</v>
+      </c>
+      <c r="D192" s="2">
+        <v>90</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A193" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B193" s="1">
+        <v>52.5</v>
+      </c>
+      <c r="C193" s="1">
+        <v>26.5</v>
+      </c>
+      <c r="D193" s="1">
+        <v>90</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A194" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B194" s="2">
+        <v>58.2</v>
+      </c>
+      <c r="C194" s="2">
+        <v>25.3</v>
+      </c>
+      <c r="D194" s="2">
+        <v>90</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A195" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B195" s="1">
+        <v>69.5</v>
+      </c>
+      <c r="C195" s="1">
+        <v>25.7</v>
+      </c>
+      <c r="D195" s="1">
+        <v>90</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A196" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B196" s="2">
+        <v>84</v>
+      </c>
+      <c r="C196" s="2">
+        <v>27</v>
+      </c>
+      <c r="D196" s="2">
+        <v>90</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A197" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B197" s="1">
+        <v>3</v>
+      </c>
+      <c r="C197" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="D197" s="1">
+        <v>90</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A198" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B198" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="C198" s="2">
+        <v>22.5</v>
+      </c>
+      <c r="D198" s="2">
+        <v>90</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A199" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B199" s="1">
+        <v>16.5</v>
+      </c>
+      <c r="C199" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="D199" s="1">
+        <v>90</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A200" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B200" s="2">
+        <v>25.5</v>
+      </c>
+      <c r="C200" s="2">
+        <v>22.5</v>
+      </c>
+      <c r="D200" s="2">
+        <v>90</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A201" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B201" s="1">
+        <v>34.5</v>
+      </c>
+      <c r="C201" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="D201" s="1">
+        <v>90</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A202" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B202" s="2">
+        <v>39</v>
+      </c>
+      <c r="C202" s="2">
+        <v>22.5</v>
+      </c>
+      <c r="D202" s="2">
+        <v>90</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A203" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B203" s="1">
+        <v>48</v>
+      </c>
+      <c r="C203" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="D203" s="1">
+        <v>90</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A204" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B204" s="2">
+        <v>52.5</v>
+      </c>
+      <c r="C204" s="2">
+        <v>22.5</v>
+      </c>
+      <c r="D204" s="2">
+        <v>90</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A205" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B205" s="1">
+        <v>61.5</v>
+      </c>
+      <c r="C205" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="D205" s="1">
+        <v>90</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A206" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B206" s="2">
+        <v>66</v>
+      </c>
+      <c r="C206" s="2">
+        <v>22.5</v>
+      </c>
+      <c r="D206" s="2">
+        <v>90</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A207" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B207" s="1">
+        <v>84</v>
+      </c>
+      <c r="C207" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="D207" s="1">
+        <v>90</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A208" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B208" s="2">
+        <v>3</v>
+      </c>
+      <c r="C208" s="2">
+        <v>18</v>
+      </c>
+      <c r="D208" s="2">
+        <v>90</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A209" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B209" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="C209" s="1">
+        <v>18</v>
+      </c>
+      <c r="D209" s="1">
+        <v>90</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A210" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B210" s="2">
+        <v>12</v>
+      </c>
+      <c r="C210" s="2">
+        <v>18</v>
+      </c>
+      <c r="D210" s="2">
+        <v>90</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A211" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B211" s="1">
+        <v>16.5</v>
+      </c>
+      <c r="C211" s="1">
+        <v>18</v>
+      </c>
+      <c r="D211" s="1">
+        <v>90</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A212" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B212" s="2">
+        <v>21</v>
+      </c>
+      <c r="C212" s="2">
+        <v>18</v>
+      </c>
+      <c r="D212" s="2">
+        <v>90</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A213" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B213" s="1">
+        <v>25.5</v>
+      </c>
+      <c r="C213" s="1">
+        <v>18</v>
+      </c>
+      <c r="D213" s="1">
+        <v>90</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A214" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B214" s="2">
+        <v>30</v>
+      </c>
+      <c r="C214" s="2">
+        <v>18</v>
+      </c>
+      <c r="D214" s="2">
+        <v>90</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A215" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B215" s="1">
+        <v>34.5</v>
+      </c>
+      <c r="C215" s="1">
+        <v>18</v>
+      </c>
+      <c r="D215" s="1">
+        <v>90</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A216" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B216" s="2">
+        <v>39</v>
+      </c>
+      <c r="C216" s="2">
+        <v>18</v>
+      </c>
+      <c r="D216" s="2">
+        <v>90</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A217" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B217" s="1">
+        <v>43.5</v>
+      </c>
+      <c r="C217" s="1">
+        <v>18</v>
+      </c>
+      <c r="D217" s="1">
+        <v>90</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A218" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B218" s="2">
+        <v>48</v>
+      </c>
+      <c r="C218" s="2">
+        <v>18</v>
+      </c>
+      <c r="D218" s="2">
+        <v>90</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A219" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B219" s="1">
+        <v>52.5</v>
+      </c>
+      <c r="C219" s="1">
+        <v>18</v>
+      </c>
+      <c r="D219" s="1">
+        <v>90</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A220" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B220" s="2">
         <v>57</v>
       </c>
-      <c r="C163">
-        <v>9</v>
-      </c>
-      <c r="D163">
-        <v>0</v>
-      </c>
-      <c r="E163" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A164" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="B164" s="1">
-        <v>29</v>
-      </c>
-      <c r="C164" s="1">
+      <c r="C220" s="2">
+        <v>18</v>
+      </c>
+      <c r="D220" s="2">
+        <v>90</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A221" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B221" s="1">
+        <v>61.5</v>
+      </c>
+      <c r="C221" s="1">
+        <v>18</v>
+      </c>
+      <c r="D221" s="1">
+        <v>90</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A222" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B222" s="2">
+        <v>66</v>
+      </c>
+      <c r="C222" s="2">
+        <v>18</v>
+      </c>
+      <c r="D222" s="2">
+        <v>90</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A223" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B223" s="1">
+        <v>70.5</v>
+      </c>
+      <c r="C223" s="1">
+        <v>18</v>
+      </c>
+      <c r="D223" s="1">
+        <v>90</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A224" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B224" s="2">
+        <v>75</v>
+      </c>
+      <c r="C224" s="2">
+        <v>18</v>
+      </c>
+      <c r="D224" s="2">
+        <v>90</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A225" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B225" s="1">
+        <v>79.5</v>
+      </c>
+      <c r="C225" s="1">
+        <v>18</v>
+      </c>
+      <c r="D225" s="1">
+        <v>90</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A226" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B226" s="2">
         <v>14.5</v>
       </c>
-      <c r="D164" s="1">
-        <v>180</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F164" s="4"/>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A165" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B165" s="2">
-        <v>15</v>
-      </c>
-      <c r="C165" s="2">
-        <v>7</v>
-      </c>
-      <c r="D165" s="2">
-        <v>270</v>
-      </c>
-      <c r="E165" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F165" s="6"/>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A166" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B166" s="1">
-        <v>25</v>
-      </c>
-      <c r="C166" s="1">
-        <v>8.5</v>
-      </c>
-      <c r="D166" s="1">
-        <v>270</v>
-      </c>
-      <c r="E166" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F166" s="4"/>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A167" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="B167" s="2">
-        <v>7.5</v>
-      </c>
-      <c r="C167" s="2">
-        <v>45</v>
-      </c>
-      <c r="D167" s="2">
-        <v>90</v>
-      </c>
-      <c r="E167" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F167" s="6"/>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A168" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B168" s="1">
-        <v>45.9</v>
-      </c>
-      <c r="C168" s="1">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="D168" s="1">
-        <v>0</v>
-      </c>
-      <c r="E168" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F168" s="4"/>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A169" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="B169" s="2">
-        <v>15.9</v>
-      </c>
-      <c r="C169" s="2">
+      <c r="C226" s="2">
+        <v>13</v>
+      </c>
+      <c r="D226" s="2">
+        <v>90</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A227" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B227" s="1">
+        <v>14.5</v>
+      </c>
+      <c r="C227" s="1">
         <v>10.5</v>
       </c>
-      <c r="D169" s="2">
-        <v>90</v>
-      </c>
-      <c r="E169" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F169" s="6"/>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A170" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B170" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="C170" s="1">
-        <v>40.5</v>
-      </c>
-      <c r="D170" s="1">
-        <v>90</v>
-      </c>
-      <c r="E170" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F170" s="4"/>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A171" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="B171" s="2">
-        <v>25.5</v>
-      </c>
-      <c r="C171" s="2">
-        <v>40.5</v>
-      </c>
-      <c r="D171" s="2">
-        <v>90</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F171" s="6"/>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A172" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B172" s="1">
-        <v>34.5</v>
-      </c>
-      <c r="C172" s="1">
-        <v>40.5</v>
-      </c>
-      <c r="D172" s="1">
-        <v>90</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F172" s="4"/>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A173" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B173" s="2">
-        <v>39</v>
-      </c>
-      <c r="C173" s="2">
-        <v>40.5</v>
-      </c>
-      <c r="D173" s="2">
-        <v>90</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F173" s="6"/>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A174" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B174" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="C174" s="1">
-        <v>36</v>
-      </c>
-      <c r="D174" s="1">
-        <v>90</v>
-      </c>
-      <c r="E174" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F174" s="4"/>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A175" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="B175" s="2">
-        <v>16.5</v>
-      </c>
-      <c r="C175" s="2">
-        <v>36</v>
-      </c>
-      <c r="D175" s="2">
-        <v>90</v>
-      </c>
-      <c r="E175" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F175" s="6"/>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A176" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B176" s="1">
-        <v>25.5</v>
-      </c>
-      <c r="C176" s="1">
-        <v>36</v>
-      </c>
-      <c r="D176" s="1">
-        <v>90</v>
-      </c>
-      <c r="E176" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F176" s="4"/>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A177" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="B177" s="2">
-        <v>34.5</v>
-      </c>
-      <c r="C177" s="2">
-        <v>36</v>
-      </c>
-      <c r="D177" s="2">
-        <v>90</v>
-      </c>
-      <c r="E177" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F177" s="6"/>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A178" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B178" s="1">
-        <v>39</v>
-      </c>
-      <c r="C178" s="1">
-        <v>36</v>
-      </c>
-      <c r="D178" s="1">
-        <v>90</v>
-      </c>
-      <c r="E178" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F178" s="4"/>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A179" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="B179" s="2">
-        <v>7.5</v>
-      </c>
-      <c r="C179" s="2">
-        <v>31.5</v>
-      </c>
-      <c r="D179" s="2">
-        <v>90</v>
-      </c>
-      <c r="E179" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F179" s="6"/>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A180" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B180" s="1">
-        <v>12</v>
-      </c>
-      <c r="C180" s="1">
-        <v>31.5</v>
-      </c>
-      <c r="D180" s="1">
-        <v>90</v>
-      </c>
-      <c r="E180" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F180" s="4"/>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A181" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="B181" s="2">
-        <v>16.5</v>
-      </c>
-      <c r="C181" s="2">
-        <v>31.5</v>
-      </c>
-      <c r="D181" s="2">
-        <v>90</v>
-      </c>
-      <c r="E181" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F181" s="6"/>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A182" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B182" s="1">
-        <v>21</v>
-      </c>
-      <c r="C182" s="1">
-        <v>31.5</v>
-      </c>
-      <c r="D182" s="1">
-        <v>90</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F182" s="4"/>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A183" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="B183" s="2">
-        <v>25.5</v>
-      </c>
-      <c r="C183" s="2">
-        <v>31.5</v>
-      </c>
-      <c r="D183" s="2">
-        <v>90</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F183" s="6"/>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A184" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="B184" s="1">
-        <v>34.5</v>
-      </c>
-      <c r="C184" s="1">
-        <v>31.5</v>
-      </c>
-      <c r="D184" s="1">
-        <v>90</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F184" s="4"/>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A185" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="B185" s="2">
-        <v>39</v>
-      </c>
-      <c r="C185" s="2">
-        <v>31.5</v>
-      </c>
-      <c r="D185" s="2">
-        <v>90</v>
-      </c>
-      <c r="E185" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F185" s="6"/>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A186" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B186" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="C186" s="1">
-        <v>27</v>
-      </c>
-      <c r="D186" s="1">
-        <v>90</v>
-      </c>
-      <c r="E186" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F186" s="4"/>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A187" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="B187" s="2">
-        <v>16.5</v>
-      </c>
-      <c r="C187" s="2">
-        <v>27</v>
-      </c>
-      <c r="D187" s="2">
-        <v>90</v>
-      </c>
-      <c r="E187" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F187" s="6"/>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A188" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B188" s="1">
-        <v>25.5</v>
-      </c>
-      <c r="C188" s="1">
-        <v>27</v>
-      </c>
-      <c r="D188" s="1">
-        <v>90</v>
-      </c>
-      <c r="E188" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F188" s="4"/>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A189" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="B189" s="2">
-        <v>30</v>
-      </c>
-      <c r="C189" s="2">
-        <v>27</v>
-      </c>
-      <c r="D189" s="2">
-        <v>90</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F189" s="6"/>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A190" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B190" s="1">
-        <v>34.5</v>
-      </c>
-      <c r="C190" s="1">
-        <v>27</v>
-      </c>
-      <c r="D190" s="1">
-        <v>90</v>
-      </c>
-      <c r="E190" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F190" s="4"/>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A191" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="B191" s="2">
-        <v>39</v>
-      </c>
-      <c r="C191" s="2">
-        <v>27</v>
-      </c>
-      <c r="D191" s="2">
-        <v>90</v>
-      </c>
-      <c r="E191" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F191" s="6"/>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A192" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B192" s="1">
-        <v>52.5</v>
-      </c>
-      <c r="C192" s="1">
-        <v>26.5</v>
-      </c>
-      <c r="D192" s="1">
-        <v>90</v>
-      </c>
-      <c r="E192" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F192" s="4"/>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A193" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B193" s="2">
-        <v>58.2</v>
-      </c>
-      <c r="C193" s="2">
-        <v>25.3</v>
-      </c>
-      <c r="D193" s="2">
-        <v>90</v>
-      </c>
-      <c r="E193" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F193" s="6"/>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A194" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="B194" s="1">
-        <v>69.5</v>
-      </c>
-      <c r="C194" s="1">
-        <v>25.7</v>
-      </c>
-      <c r="D194" s="1">
-        <v>90</v>
-      </c>
-      <c r="E194" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F194" s="4"/>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A195" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="B195" s="2">
-        <v>84</v>
-      </c>
-      <c r="C195" s="2">
-        <v>27</v>
-      </c>
-      <c r="D195" s="2">
-        <v>90</v>
-      </c>
-      <c r="E195" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F195" s="6"/>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A196" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="B196" s="1">
-        <v>3</v>
-      </c>
-      <c r="C196" s="1">
-        <v>22.5</v>
-      </c>
-      <c r="D196" s="1">
-        <v>90</v>
-      </c>
-      <c r="E196" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F196" s="4"/>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A197" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="B197" s="2">
-        <v>7.5</v>
-      </c>
-      <c r="C197" s="2">
-        <v>22.5</v>
-      </c>
-      <c r="D197" s="2">
-        <v>90</v>
-      </c>
-      <c r="E197" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F197" s="6"/>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A198" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B198" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="C198" s="1">
-        <v>22.5</v>
-      </c>
-      <c r="D198" s="1">
-        <v>90</v>
-      </c>
-      <c r="E198" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F198" s="4"/>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A199" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="B199" s="2">
-        <v>25.5</v>
-      </c>
-      <c r="C199" s="2">
-        <v>22.5</v>
-      </c>
-      <c r="D199" s="2">
-        <v>90</v>
-      </c>
-      <c r="E199" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F199" s="6"/>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A200" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="B200" s="1">
-        <v>34.5</v>
-      </c>
-      <c r="C200" s="1">
-        <v>22.5</v>
-      </c>
-      <c r="D200" s="1">
-        <v>90</v>
-      </c>
-      <c r="E200" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F200" s="4"/>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A201" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="B201" s="2">
-        <v>39</v>
-      </c>
-      <c r="C201" s="2">
-        <v>22.5</v>
-      </c>
-      <c r="D201" s="2">
-        <v>90</v>
-      </c>
-      <c r="E201" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F201" s="6"/>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A202" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="B202" s="1">
-        <v>48</v>
-      </c>
-      <c r="C202" s="1">
-        <v>22.5</v>
-      </c>
-      <c r="D202" s="1">
-        <v>90</v>
-      </c>
-      <c r="E202" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F202" s="4"/>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A203" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="B203" s="2">
-        <v>52.5</v>
-      </c>
-      <c r="C203" s="2">
-        <v>22.5</v>
-      </c>
-      <c r="D203" s="2">
-        <v>90</v>
-      </c>
-      <c r="E203" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F203" s="6"/>
-    </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A204" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B204" s="1">
-        <v>61.5</v>
-      </c>
-      <c r="C204" s="1">
-        <v>22.5</v>
-      </c>
-      <c r="D204" s="1">
-        <v>90</v>
-      </c>
-      <c r="E204" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F204" s="4"/>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A205" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="B205" s="2">
-        <v>66</v>
-      </c>
-      <c r="C205" s="2">
-        <v>22.5</v>
-      </c>
-      <c r="D205" s="2">
-        <v>90</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F205" s="6"/>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A206" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="B206" s="1">
-        <v>84</v>
-      </c>
-      <c r="C206" s="1">
-        <v>22.5</v>
-      </c>
-      <c r="D206" s="1">
-        <v>90</v>
-      </c>
-      <c r="E206" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F206" s="4"/>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A207" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="B207" s="2">
-        <v>3</v>
-      </c>
-      <c r="C207" s="2">
-        <v>18</v>
-      </c>
-      <c r="D207" s="2">
-        <v>90</v>
-      </c>
-      <c r="E207" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F207" s="6"/>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A208" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B208" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="C208" s="1">
-        <v>18</v>
-      </c>
-      <c r="D208" s="1">
-        <v>90</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F208" s="4"/>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A209" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="B209" s="2">
-        <v>12</v>
-      </c>
-      <c r="C209" s="2">
-        <v>18</v>
-      </c>
-      <c r="D209" s="2">
-        <v>90</v>
-      </c>
-      <c r="E209" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F209" s="6"/>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A210" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B210" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="C210" s="1">
-        <v>18</v>
-      </c>
-      <c r="D210" s="1">
-        <v>90</v>
-      </c>
-      <c r="E210" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F210" s="4"/>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A211" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="B211" s="2">
-        <v>21</v>
-      </c>
-      <c r="C211" s="2">
-        <v>18</v>
-      </c>
-      <c r="D211" s="2">
-        <v>90</v>
-      </c>
-      <c r="E211" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F211" s="6"/>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A212" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B212" s="1">
-        <v>25.5</v>
-      </c>
-      <c r="C212" s="1">
-        <v>18</v>
-      </c>
-      <c r="D212" s="1">
-        <v>90</v>
-      </c>
-      <c r="E212" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F212" s="4"/>
-    </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A213" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="B213" s="2">
-        <v>30</v>
-      </c>
-      <c r="C213" s="2">
-        <v>18</v>
-      </c>
-      <c r="D213" s="2">
-        <v>90</v>
-      </c>
-      <c r="E213" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F213" s="6"/>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A214" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="B214" s="1">
-        <v>34.5</v>
-      </c>
-      <c r="C214" s="1">
-        <v>18</v>
-      </c>
-      <c r="D214" s="1">
-        <v>90</v>
-      </c>
-      <c r="E214" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F214" s="4"/>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A215" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B215" s="2">
-        <v>39</v>
-      </c>
-      <c r="C215" s="2">
-        <v>18</v>
-      </c>
-      <c r="D215" s="2">
-        <v>90</v>
-      </c>
-      <c r="E215" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F215" s="6"/>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A216" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B216" s="1">
-        <v>43.5</v>
-      </c>
-      <c r="C216" s="1">
-        <v>18</v>
-      </c>
-      <c r="D216" s="1">
-        <v>90</v>
-      </c>
-      <c r="E216" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F216" s="4"/>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A217" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="B217" s="2">
-        <v>48</v>
-      </c>
-      <c r="C217" s="2">
-        <v>18</v>
-      </c>
-      <c r="D217" s="2">
-        <v>90</v>
-      </c>
-      <c r="E217" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F217" s="6"/>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A218" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B218" s="1">
-        <v>52.5</v>
-      </c>
-      <c r="C218" s="1">
-        <v>18</v>
-      </c>
-      <c r="D218" s="1">
-        <v>90</v>
-      </c>
-      <c r="E218" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F218" s="4"/>
-    </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A219" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="B219" s="2">
-        <v>57</v>
-      </c>
-      <c r="C219" s="2">
-        <v>18</v>
-      </c>
-      <c r="D219" s="2">
-        <v>90</v>
-      </c>
-      <c r="E219" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F219" s="6"/>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A220" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B220" s="1">
-        <v>61.5</v>
-      </c>
-      <c r="C220" s="1">
-        <v>18</v>
-      </c>
-      <c r="D220" s="1">
-        <v>90</v>
-      </c>
-      <c r="E220" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F220" s="4"/>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A221" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="B221" s="2">
-        <v>66</v>
-      </c>
-      <c r="C221" s="2">
-        <v>18</v>
-      </c>
-      <c r="D221" s="2">
-        <v>90</v>
-      </c>
-      <c r="E221" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F221" s="6"/>
-    </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A222" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B222" s="1">
-        <v>70.5</v>
-      </c>
-      <c r="C222" s="1">
-        <v>18</v>
-      </c>
-      <c r="D222" s="1">
-        <v>90</v>
-      </c>
-      <c r="E222" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F222" s="4"/>
-    </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A223" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="B223" s="2">
-        <v>75</v>
-      </c>
-      <c r="C223" s="2">
-        <v>18</v>
-      </c>
-      <c r="D223" s="2">
-        <v>90</v>
-      </c>
-      <c r="E223" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F223" s="6"/>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A224" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B224" s="1">
-        <v>79.5</v>
-      </c>
-      <c r="C224" s="1">
-        <v>18</v>
-      </c>
-      <c r="D224" s="1">
-        <v>90</v>
-      </c>
-      <c r="E224" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F224" s="4"/>
-    </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A225" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="B225" s="2">
-        <v>14.5</v>
-      </c>
-      <c r="C225" s="2">
-        <v>13</v>
-      </c>
-      <c r="D225" s="2">
-        <v>90</v>
-      </c>
-      <c r="E225" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F225" s="6"/>
-    </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A226" s="3" t="s">
+      <c r="D227" s="1">
+        <v>90</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A228" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="B226" s="1">
-        <v>14.5</v>
-      </c>
-      <c r="C226" s="1">
-        <v>10.5</v>
-      </c>
-      <c r="D226" s="1">
-        <v>90</v>
-      </c>
-      <c r="E226" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F226" s="4"/>
-    </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A227" s="5" t="s">
+      <c r="B228" s="2">
+        <v>33.5</v>
+      </c>
+      <c r="C228" s="2">
+        <v>12.2</v>
+      </c>
+      <c r="D228" s="2">
+        <v>0</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A229" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B227" s="2">
-        <v>33.5</v>
-      </c>
-      <c r="C227" s="2">
-        <v>12.2</v>
-      </c>
-      <c r="D227" s="2">
-        <v>0</v>
-      </c>
-      <c r="E227" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F227" s="6"/>
-    </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A228" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="B228" s="1">
+      <c r="B229" s="1">
         <v>40</v>
       </c>
-      <c r="C228" s="1">
+      <c r="C229" s="1">
         <v>12.4</v>
       </c>
-      <c r="D228" s="1">
-        <v>90</v>
-      </c>
-      <c r="E228" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F228" s="4"/>
+      <c r="D229" s="1">
+        <v>90</v>
+      </c>
+      <c r="E229" s="1" t="s">
+        <v>230</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
